--- a/Documentation/Best For Lists/Best Pets for Seniors in Memory Care Facilities List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors in Memory Care Facilities List.xlsx
@@ -605,7 +605,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-12  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-15  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Seniors in Memory Care Facilities List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors in Memory Care Facilities List.xlsx
@@ -1510,22 +1510,20 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Dog</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>25.99</v>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I17" s="9" t="n">
         <v>3.3</v>

--- a/Documentation/Best For Lists/Best Pets for Seniors in Memory Care Facilities List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors in Memory Care Facilities List.xlsx
@@ -605,7 +605,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-15  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-16  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Seniors in Memory Care Facilities List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors in Memory Care Facilities List.xlsx
@@ -1465,10 +1465,10 @@
         <v>17</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>4</v>

--- a/Documentation/Best For Lists/Best Pets for Seniors in Memory Care Facilities List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors in Memory Care Facilities List.xlsx
@@ -605,7 +605,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-16  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-08-10  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="F5" s="8" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>3.95</v>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>3.95</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Border Collie</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
         <v>44.45</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>848</v>
+        <v>441</v>
       </c>
       <c r="I8" s="13" t="n">
         <v>3.9</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Q8" s="11" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Previously scored as 'Calico Cat' — now matched to 'Grey Tabby Cat' per repo. Verify this is the correct product match before publishing. Review Strength=4: 848 reviews, 4.3★ (repo data, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Border Collie' per repo. Review Strength=3: 403 reviews, 4.3★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="F9" s="8" t="n">
-        <v>44.45</v>
+        <v>53.9</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>553</v>
+        <v>55</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>3.9</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Chocolate Lab' per repo. Review Strength=4: 553 reviews, 4.3★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. White coat: higher visual contrast against most furniture/bedding. Product name updated: 'Original Plush White Cat' per repo. Review Strength=2: 54 reviews, 4.0★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>50.11</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>772</v>
+        <v>1132</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>3.75</v>
@@ -1210,7 +1210,7 @@
         <v>4.5</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>11640</v>
+        <v>12310</v>
       </c>
       <c r="I12" s="13" t="n">
         <v>3.75</v>
@@ -1273,7 +1273,7 @@
         <v>4.3</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>5164</v>
+        <v>5195</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>3.75</v>
@@ -1333,10 +1333,10 @@
         <v>69.98999999999999</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>283</v>
+        <v>346</v>
       </c>
       <c r="I14" s="13" t="n">
         <v>3.55</v>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>5</v>
@@ -1459,10 +1459,10 @@
         <v>349</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I16" s="13" t="n">
         <v>3.5</v>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>5</v>
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>4.5</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>3.05</v>
@@ -1709,10 +1709,10 @@
         <v>499</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>1199</v>
+        <v>1231</v>
       </c>
       <c r="I20" s="14" t="n">
         <v>2.85</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>MateCat Pro</t>
+          <t>MateCat 1.1</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
@@ -1847,7 +1847,7 @@
         <v>3.95</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="G3" s="16" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>score=3.95 rating=4.6</t>
+          <t>score=3.95 rating=4.95</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>MateCat 1.1</t>
+          <t>MateCat Pro</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
@@ -1885,7 +1885,7 @@
         <v>3.95</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>score=3.95 rating=4</t>
+          <t>score=3.95 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>Original Siamese Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -1923,16 +1923,16 @@
         <v>3.9</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>score=3.90 rating=4.1</t>
+          <t>score=3.90 rating=4.2</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Original Plush White Cat</t>
+          <t>Original Siamese Cat</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -1961,16 +1961,16 @@
         <v>3.9</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>score=3.90 rating=4</t>
+          <t>score=3.90 rating=4.1</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>Original Border Collie</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G9" s="16" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Border Collie</t>
         </is>
       </c>
       <c r="H9" s="16" t="inlineStr">

--- a/Documentation/Best For Lists/Best Pets for Seniors in Memory Care Facilities List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Seniors in Memory Care Facilities List.xlsx
@@ -605,7 +605,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-10  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-08-13  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>
